--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0008.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0008.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Total Points: {0}</t>
+          <t>Tổng Điểm: {0}</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Suggested Lv. {0}</t>
+          <t>Cấp đề xuất: {0}</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Souvenir Cửa hàng&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Cửa Hàng Lưu Niệm&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Thus Says the Moon&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Vầng Trăng Phán Xử&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Riddle Twiddle&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Đố Vui Đãi Não&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Fan Drawing Stall&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Gian Hàng Tranh Fan&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Plum Blossom Pole&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Cột Hoa Mai&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Wishing Stall&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Gian Hàng Ước Nguyện&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Puppet Theater&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Nhà Hát Múa Rối&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Yumyum Haven&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Thiên Đường Ẩm Thực&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Hsin's Fortuity&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;May Mắn Của Hsin&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Fireworks Shop&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Cửa Hàng Pháo Hoa&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Wishing Stall&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Gian Hàng Ước Nguyện&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Swim, Gulpuff, Swim&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Bơi Đi, Gulpuff, Bơi!&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;KU-Money Exchange&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Đổi Tiền KU&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Retro Game Collector&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Nhà Sưu Tầm Game Cổ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Monnaie Retrieval &amp; Exchange&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Thu Hồi &amp; Đổi Tiền Monnaie&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Averardo Bank Counter&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Quầy Giao Dịch Averardo&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Grocery Cửa hàng&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Cửa Hàng Tạp Hóa&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Pharmacy Cửa hàng [Rosemary's Apothecary]&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Hiệu Thuốc [Rosemary's Apothecary]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Trattoria Margherita&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Nhà Hàng Trattoria Margherita&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Stillwind Sundries&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Tạp Hóa Stillwind&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Burrata Bakery&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Tiệm Bánh Burrata&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Masks &amp; Garments [Masked Reverie]&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Mặt Nạ &amp; Trang Phục [Mộng Ảo]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Rinascita Sonance Casket Collector&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Người Thu Thập Hòm Sonance Rinascita&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Pioneer Association&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Hiệp Hội Tiên Phong&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Archive of Melodies&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Bảo Tàng Giai Điệu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Synthesizer&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Máy Tổng Hợp&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Wave Cleared&lt;/color&gt;</t>
+          <t>&lt;color=#ffd12f&gt;Đã Dọn Sóng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả sẽ hồi sinh sau {0}</t>
+          <t>Resonator sẽ hồi sinh sau {0}</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>{0} nữa Cộng Hưởng Giả của Người Chơi 1 sẽ hồi sinh.</t>
+          <t>{0} nữa Resonator của Người Chơi 1 sẽ hồi sinh.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả dưới cấp {0} sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên {0}.</t>
+          <t>Resonator dưới cấp {0} sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên {0}.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Dùng để mở khóa trang phục đặc trưng của Cộng Hưởng Giả, giúp nhân vật có diện mạo mới</t>
+          <t>Dùng để mở khóa trang phục đặc trưng của Resonator, giúp nhân vật có diện mạo mới</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Tất cả Cộng Hưởng Giả có thể chiêu mộ trong cửa hàng này đều đã được tuyển dụng.</t>
+          <t>Tất cả Resonator có thể chiêu mộ trong cửa hàng này đều đã được tuyển dụng.</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>{0}&lt;color=#6a7b84&gt;/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>&lt;color=#f9ffffcc&gt;Overlord | Calamity&lt;/color&gt;</t>
+          <t>&lt;color=#f9ffffcc&gt;Thống Trị | Tai Họa&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>&lt;color=#f9ffffcc&gt;- Remaining Chances&lt;/color&gt;</t>
+          <t>&lt;color=#f9ffffcc&gt;- Cơ Hội Còn Lại&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>&lt;color=#f4f2bfff&gt;{0}&lt;/color&gt;&lt;color=#f9ffff7f&gt;/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Đã mở khóa &lt;color=#ffd12f&gt;Khó Mode&lt;/color&gt;.</t>
+          <t>Đã mở khóa &lt;color=#ffd12f&gt;Chế Độ Khó&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;Here, the sword points at the space.&lt;/color&gt;
+          <t>&lt;color=#c49e55&gt;Nơi đây, lưỡi kiếm chĩa vào không gian.&lt;/color&gt;
 Hoàn thành Nhiệm Vụ Phụ "Dấu Chân Trên Vùng Đất Băng Giá" để nhận.</t>
         </is>
       </c>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;Here, the flows of information converge.&lt;/color&gt;
+          <t>&lt;color=#c49e55&gt;Nơi đây, thông tin chảy về một mối.&lt;/color&gt;
 Hoàn thành Nhiệm Vụ Phụ "Dấu Chân Trên Vùng Đất Băng Giá" để nhận.</t>
         </is>
       </c>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;Here, the dream is frozen in time.&lt;/color&gt;
+          <t>&lt;color=#c49e55&gt;Nơi đây, giấc mơ bị đóng băng theo thời gian.&lt;/color&gt;
 Hoàn thành Nhiệm Vụ Phụ "Dấu Chân Trên Vùng Đất Băng Giá" để nhận.</t>
         </is>
       </c>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;Here, the ice seals the bygone days.&lt;/color&gt;
+          <t>&lt;color=#c49e55&gt;Nơi đây, băng giá niêm phong những ngày đã qua.&lt;/color&gt;
 Hoàn thành Nhiệm Vụ Phụ "Dấu Chân Trên Vùng Đất Băng Giá" để nhận.</t>
         </is>
       </c>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Cantarella&lt;/color&gt; đang nếm thử các món ăn. Liệu vị giác của cô ấy đã trở lại chưa? Hãy đến trò chuyện với cô ấy tại &lt;color=Highlight&gt;Bar&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Cantarella&lt;/color&gt; đang nếm thử các món ăn. Liệu vị giác của cô ấy đã trở lại chưa? Hãy đến trò chuyện với cô ấy tại &lt;color=Highlight&gt;Quầy Bar&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Khi Bản Nhạc Đã Quen!</t>
+          <t>Khi Âm Thức Đã Biết vang lên!</t>
         </is>
       </c>
     </row>
@@ -15215,7 +15215,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Huấn luyện tuy vất vả, nhưng xứng đáng lắm! Ta sẽ cố hết sức!</t>
+          <t>Huấn luyện tuy vất vả, nhưng xứng đáng lắm! Tao sẽ cố hết sức!</t>
         </is>
       </c>
     </row>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Tiền bối có thích chim không?</t>
+          <t>bạn có thích chim không?</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Tiền bối có thể ở lại với em thêm chút nữa không?</t>
+          <t>bạn có thể ở lại với em thêm chút nữa không?</t>
         </is>
       </c>
     </row>
@@ -16782,7 +16782,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Nơi &lt;color=#c49e55&gt;Where the past was sealed away&lt;/color&gt;
+          <t>Nơi &lt;color=#c49e55&gt;quá khứ bị phong ấn&lt;/color&gt;
 Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Chuyến Đi Tốt Nghiệp".</t>
         </is>
       </c>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Nơi &lt;color=#c49e55&gt;Where the foreclaiming decision was made&lt;/color&gt;
+          <t>Nơi &lt;color=#c49e55&gt;quyết định tiên đoán được đưa ra&lt;/color&gt;
 Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Chuyến Đi Tốt Nghiệp".</t>
         </is>
       </c>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Nơi &lt;color=#c49e55&gt;Where the Exostrider stands guard&lt;/color&gt;
+          <t>Nơi &lt;color=#c49e55&gt;Exostrider đứng canh giữ&lt;/color&gt;
 Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Chuyến Đi Tốt Nghiệp".</t>
         </is>
       </c>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>&lt;color=#fff29d&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Đội của cậu có ít hơn 3 Cộng Hưởng Giả. Vẫn bắt đầu bài kiểm tra chứ?</t>
+          <t>Đội của cậu có ít hơn 3 Resonator. Vẫn bắt đầu bài kiểm tra chứ?</t>
         </is>
       </c>
     </row>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Chỉ số của các Cộng Hưởng Giả trong đội được tăng cường.</t>
+          <t>Chỉ số của các Resonator trong đội được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>&lt;color=#182b34&gt;{0}&lt;/color&gt;&lt;color=#6a7b84&gt;/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -21081,7 +21081,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>&lt;color=#f4f2bf&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>{0}&lt;color=#657584&gt;/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -23098,7 +23098,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Nền tảng Tổng hợp của Học viện cho phép Cộng Hưởng Giả dễ dàng chế tạo thuốc dược, vật liệu xây dựng và tinh luyện các chất.</t>
+          <t>Nền tảng Tổng hợp của Học viện cho phép Resonator dễ dàng chế tạo thuốc dược, vật liệu xây dựng và tinh luyện các chất.</t>
         </is>
       </c>
     </row>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Cửa hàng bán đa dạng dược phẩm, bạn có thể tìm thấy các loại thuốc chữa bệnh hàng ngày cần thiết tại đây.</t>
+          <t>Cửa hàng bán nhiều loại dược phẩm, bạn có thể tìm thấy các loại thuốc chữa bệnh hàng ngày cần thiết tại đây.</t>
         </is>
       </c>
     </row>
@@ -24333,7 +24333,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Tại rìa Núi Firmament, tiếng sóng vỗ vọng từ những tàn tích ven biển.</t>
+          <t>Bên rìa núi Firmament, tiếng vọng triều dâng từ những tàn tích ven biển.</t>
         </is>
       </c>
     </row>
@@ -24463,7 +24463,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Nhảy Nhảy Chelonian!</t>
+          <t>Vũ điệu Rùa Chelonian!</t>
         </is>
       </c>
     </row>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament I</t>
+          <t>Dấu vết Núi Firmament I</t>
         </is>
       </c>
     </row>
@@ -24593,7 +24593,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament II</t>
+          <t>Dấu vết Núi Firmament II</t>
         </is>
       </c>
     </row>
@@ -24658,7 +24658,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament III</t>
+          <t>Dấu vết Núi Firmament III</t>
         </is>
       </c>
     </row>
@@ -24723,7 +24723,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament IV</t>
+          <t>Dấu vết Núi Firmament IV</t>
         </is>
       </c>
     </row>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament V</t>
+          <t>Dấu vết Núi Firmament V</t>
         </is>
       </c>
     </row>
@@ -24853,7 +24853,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament VI</t>
+          <t>Dấu vết Núi Firmament VI</t>
         </is>
       </c>
     </row>
@@ -24918,7 +24918,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament VII</t>
+          <t>Dấu vết Núi Firmament VII</t>
         </is>
       </c>
     </row>
@@ -24983,7 +24983,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament VIII</t>
+          <t>Dấu vết Núi Firmament VIII</t>
         </is>
       </c>
     </row>
@@ -25048,7 +25048,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament IX</t>
+          <t>Dấu vết Núi Firmament IX</t>
         </is>
       </c>
     </row>
@@ -25113,7 +25113,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Trên những vách đá cao chót vót vươn lên trời, một con rồng thực sự xuất hiện từ trong mây.</t>
+          <t>Trên những vách đá cao chót vót vươn lên trời, một con rồng đích thực hiện ra từ trong mây.</t>
         </is>
       </c>
     </row>
@@ -25178,7 +25178,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Ánh đèn mờ ảo tỏa sáng dịu dàng trên mặt hồ khi tuyết rơi nhẹ từ bầu trời.</t>
+          <t>Ánh sáng mờ ảo phủ lên mặt hồ khi tuyết rơi nhẹ từ bầu trời.</t>
         </is>
       </c>
     </row>
@@ -25243,7 +25243,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Theo lời các bậc trưởng lão ở Hồng Trấn, cảnh quan kỳ bí ấy, tựa như xương rồng, có mối liên hệ sâu sắc với Jué.</t>
+          <t>Theo lời các bậc trưởng lão ở Hongzhen, cảnh quan kỳ bí ấy, tựa như xương rồng, có mối liên hệ sâu sắc với Jué.</t>
         </is>
       </c>
     </row>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Nước trong hồ sâu dường như ngưng tụ khi một lối vào hang động mở ra.</t>
+          <t>Nước trong hồ sâu dường như ngưng tụ lại khi lối vào hố sâu mở ra.</t>
         </is>
       </c>
     </row>
@@ -25568,7 +25568,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Tại rìa Núi Firmament, tiếng sóng vỗ vọng từ những tàn tích ven biển.</t>
+          <t>Bên rìa núi Firmament, tiếng vọng triều dâng từ những tàn tích ven biển.</t>
         </is>
       </c>
     </row>
@@ -29240,7 +29240,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Tạo ra dòng trọng lực sau khi sử dụng &lt;color=highlight&gt;Echo Skills&lt;/color&gt;.</t>
+          <t>Tạo ra dòng trọng lực sau khi sử dụng &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Lv. {0}&lt;/color&gt;</t>
+          <t>&lt;color=Highlight&gt;Cấp {0}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
